--- a/research/traditional_assets/database/data/costa_rica/costa_rica_healthcare_products.xlsx
+++ b/research/traditional_assets/database/data/costa_rica/costa_rica_healthcare_products.xlsx
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.06677937447168218</v>
+        <v>-0.010443864229765</v>
       </c>
       <c r="H2">
-        <v>-0.2079459002535926</v>
+        <v>-0.1396866840731071</v>
       </c>
       <c r="I2">
-        <v>-0.2003418479806427</v>
+        <v>-0.2332229131649577</v>
       </c>
       <c r="J2">
-        <v>-0.2003418479806427</v>
+        <v>-0.2332229131649577</v>
       </c>
       <c r="K2">
-        <v>-32.6</v>
+        <v>-75.8</v>
       </c>
       <c r="L2">
-        <v>-0.275570583262891</v>
+        <v>-0.4947780678851175</v>
       </c>
       <c r="M2">
-        <v>0.177</v>
+        <v>0.273</v>
       </c>
       <c r="N2">
-        <v>0.0001090976331360947</v>
+        <v>0.0001708278580814718</v>
       </c>
       <c r="O2">
-        <v>-0.005429447852760736</v>
+        <v>-0.003601583113456465</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +624,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.177</v>
+        <v>0.273</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>64.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="V2">
-        <v>0.03981755424063116</v>
+        <v>0.04086102246417621</v>
       </c>
       <c r="W2">
-        <v>-0.4075</v>
+        <v>-1.23051948051948</v>
       </c>
       <c r="X2">
-        <v>0.11223632881619</v>
+        <v>0.2160435956733699</v>
       </c>
       <c r="Y2">
-        <v>-0.51973632881619</v>
+        <v>-1.44656307619285</v>
       </c>
       <c r="Z2">
-        <v>2.34061819211685</v>
+        <v>3.070217098478416</v>
       </c>
       <c r="AA2">
-        <v>-0.4689237740258008</v>
+        <v>-0.716044975756</v>
       </c>
       <c r="AB2">
-        <v>0.1103001747749395</v>
+        <v>0.2048403632329535</v>
       </c>
       <c r="AC2">
-        <v>-0.5792239488007404</v>
+        <v>-0.9208853389889535</v>
       </c>
       <c r="AD2">
-        <v>51.4</v>
+        <v>148.2</v>
       </c>
       <c r="AE2">
-        <v>2.807203080550166</v>
+        <v>1.963751484357608</v>
       </c>
       <c r="AF2">
-        <v>54.20720308055017</v>
+        <v>150.1637514843576</v>
       </c>
       <c r="AG2">
-        <v>-10.39279691944983</v>
+        <v>84.86375148435759</v>
       </c>
       <c r="AH2">
-        <v>0.03233148645726405</v>
+        <v>0.08589307612015724</v>
       </c>
       <c r="AI2">
-        <v>0.4680814460465479</v>
+        <v>0.9899791507981212</v>
       </c>
       <c r="AJ2">
-        <v>-0.006447115682603134</v>
+        <v>0.0504251808213389</v>
       </c>
       <c r="AK2">
-        <v>-0.2029557619677393</v>
+        <v>0.982404098295323</v>
       </c>
       <c r="AL2">
-        <v>8.949999999999999</v>
+        <v>11.9</v>
       </c>
       <c r="AM2">
-        <v>8.931999999999999</v>
+        <v>11.83</v>
       </c>
       <c r="AN2">
-        <v>-2.630636163570296</v>
+        <v>-4.699242160002536</v>
       </c>
       <c r="AO2">
-        <v>-2.659217877094972</v>
+        <v>-3.016806722689076</v>
       </c>
       <c r="AP2">
-        <v>0.5319001442985736</v>
+        <v>-2.690926577808846</v>
       </c>
       <c r="AQ2">
-        <v>-2.664576802507837</v>
+        <v>-3.034657650042266</v>
       </c>
     </row>
     <row r="3">
@@ -716,31 +716,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.06677937447168218</v>
+        <v>-0.010443864229765</v>
       </c>
       <c r="H3">
-        <v>-0.2079459002535926</v>
+        <v>-0.1396866840731071</v>
       </c>
       <c r="I3">
-        <v>-0.2003418479806427</v>
+        <v>-0.2332229131649577</v>
       </c>
       <c r="J3">
-        <v>-0.2003418479806427</v>
+        <v>-0.2332229131649577</v>
       </c>
       <c r="K3">
-        <v>-32.6</v>
+        <v>-75.8</v>
       </c>
       <c r="L3">
-        <v>-0.275570583262891</v>
+        <v>-0.4947780678851175</v>
       </c>
       <c r="M3">
-        <v>0.177</v>
+        <v>0.273</v>
       </c>
       <c r="N3">
-        <v>0.0001090976331360947</v>
+        <v>0.0001708278580814718</v>
       </c>
       <c r="O3">
-        <v>-0.005429447852760736</v>
+        <v>-0.003601583113456465</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +752,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0.177</v>
+        <v>0.273</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>64.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="V3">
-        <v>0.03981755424063116</v>
+        <v>0.04086102246417621</v>
       </c>
       <c r="W3">
-        <v>-0.4075</v>
+        <v>-1.23051948051948</v>
       </c>
       <c r="X3">
-        <v>0.11223632881619</v>
+        <v>0.2160435956733699</v>
       </c>
       <c r="Y3">
-        <v>-0.51973632881619</v>
+        <v>-1.44656307619285</v>
       </c>
       <c r="Z3">
-        <v>2.34061819211685</v>
+        <v>3.070217098478416</v>
       </c>
       <c r="AA3">
-        <v>-0.4689237740258008</v>
+        <v>-0.716044975756</v>
       </c>
       <c r="AB3">
-        <v>0.1103001747749395</v>
+        <v>0.2048403632329535</v>
       </c>
       <c r="AC3">
-        <v>-0.5792239488007404</v>
+        <v>-0.9208853389889535</v>
       </c>
       <c r="AD3">
-        <v>51.4</v>
+        <v>148.2</v>
       </c>
       <c r="AE3">
-        <v>2.807203080550166</v>
+        <v>1.963751484357608</v>
       </c>
       <c r="AF3">
-        <v>54.20720308055017</v>
+        <v>150.1637514843576</v>
       </c>
       <c r="AG3">
-        <v>-10.39279691944983</v>
+        <v>84.86375148435759</v>
       </c>
       <c r="AH3">
-        <v>0.03233148645726405</v>
+        <v>0.08589307612015724</v>
       </c>
       <c r="AI3">
-        <v>0.4680814460465479</v>
+        <v>0.9899791507981212</v>
       </c>
       <c r="AJ3">
-        <v>-0.006447115682603134</v>
+        <v>0.0504251808213389</v>
       </c>
       <c r="AK3">
-        <v>-0.2029557619677393</v>
+        <v>0.982404098295323</v>
       </c>
       <c r="AL3">
-        <v>8.949999999999999</v>
+        <v>11.9</v>
       </c>
       <c r="AM3">
-        <v>8.931999999999999</v>
+        <v>11.83</v>
       </c>
       <c r="AN3">
-        <v>-2.630636163570296</v>
+        <v>-4.699242160002536</v>
       </c>
       <c r="AO3">
-        <v>-2.659217877094972</v>
+        <v>-3.016806722689076</v>
       </c>
       <c r="AP3">
-        <v>0.5319001442985736</v>
+        <v>-2.690926577808846</v>
       </c>
       <c r="AQ3">
-        <v>-2.664576802507837</v>
+        <v>-3.034657650042266</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/costa_rica/costa_rica_healthcare_products.xlsx
+++ b/research/traditional_assets/database/data/costa_rica/costa_rica_healthcare_products.xlsx
@@ -587,32 +587,35 @@
           <t>Healthcare Products</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.257</v>
+      </c>
       <c r="G2">
-        <v>-0.010443864229765</v>
+        <v>-0.04904171364148813</v>
       </c>
       <c r="H2">
-        <v>-0.1396866840731071</v>
+        <v>-0.201803833145434</v>
       </c>
       <c r="I2">
-        <v>-0.2332229131649577</v>
+        <v>-0.3147088145344539</v>
       </c>
       <c r="J2">
-        <v>-0.2332229131649577</v>
+        <v>-0.3147088145344539</v>
       </c>
       <c r="K2">
-        <v>-75.8</v>
+        <v>-71.5</v>
       </c>
       <c r="L2">
-        <v>-0.4947780678851175</v>
+        <v>-0.40304396843292</v>
       </c>
       <c r="M2">
-        <v>0.273</v>
+        <v>0.449</v>
       </c>
       <c r="N2">
-        <v>0.0001708278580814718</v>
+        <v>0.0006719545046393296</v>
       </c>
       <c r="O2">
-        <v>-0.003601583113456465</v>
+        <v>-0.00627972027972028</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +627,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.273</v>
+        <v>0.449</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>65.3</v>
+        <v>52.2</v>
       </c>
       <c r="V2">
-        <v>0.04086102246417621</v>
+        <v>0.07812032325651003</v>
       </c>
       <c r="W2">
-        <v>-1.23051948051948</v>
+        <v>-47.03947368421053</v>
       </c>
       <c r="X2">
-        <v>0.2160435956733699</v>
+        <v>0.1781326523680062</v>
       </c>
       <c r="Y2">
-        <v>-1.44656307619285</v>
+        <v>-47.21760633657853</v>
       </c>
       <c r="Z2">
-        <v>3.070217098478416</v>
+        <v>2.028547901161089</v>
       </c>
       <c r="AA2">
-        <v>-0.716044975756</v>
+        <v>-0.638401905200761</v>
       </c>
       <c r="AB2">
-        <v>0.2048403632329535</v>
+        <v>0.1542949650373791</v>
       </c>
       <c r="AC2">
-        <v>-0.9208853389889535</v>
+        <v>-0.7926968702381401</v>
       </c>
       <c r="AD2">
-        <v>148.2</v>
+        <v>185.3</v>
       </c>
       <c r="AE2">
-        <v>1.963751484357608</v>
+        <v>3.496718492060621</v>
       </c>
       <c r="AF2">
-        <v>150.1637514843576</v>
+        <v>188.7967184920606</v>
       </c>
       <c r="AG2">
-        <v>84.86375148435759</v>
+        <v>136.5967184920606</v>
       </c>
       <c r="AH2">
-        <v>0.08589307612015724</v>
+        <v>0.2203003983775577</v>
       </c>
       <c r="AI2">
-        <v>0.9899791507981212</v>
+        <v>0.8609190314851691</v>
       </c>
       <c r="AJ2">
-        <v>0.0504251808213389</v>
+        <v>0.1697282249708976</v>
       </c>
       <c r="AK2">
-        <v>0.982404098295323</v>
+        <v>0.8174709816252366</v>
       </c>
       <c r="AL2">
-        <v>11.9</v>
+        <v>13.3</v>
       </c>
       <c r="AM2">
-        <v>11.83</v>
+        <v>12.759</v>
       </c>
       <c r="AN2">
-        <v>-4.699242160002536</v>
+        <v>-3.624095442988461</v>
       </c>
       <c r="AO2">
-        <v>-3.016806722689076</v>
+        <v>-4.218045112781954</v>
       </c>
       <c r="AP2">
-        <v>-2.690926577808846</v>
+        <v>-2.671557177626846</v>
       </c>
       <c r="AQ2">
-        <v>-3.034657650042266</v>
+        <v>-4.396896308488126</v>
       </c>
     </row>
     <row r="3">
@@ -715,32 +718,35 @@
           <t>Healthcare Products</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.257</v>
+      </c>
       <c r="G3">
-        <v>-0.010443864229765</v>
+        <v>-0.04904171364148813</v>
       </c>
       <c r="H3">
-        <v>-0.1396866840731071</v>
+        <v>-0.201803833145434</v>
       </c>
       <c r="I3">
-        <v>-0.2332229131649577</v>
+        <v>-0.3147088145344539</v>
       </c>
       <c r="J3">
-        <v>-0.2332229131649577</v>
+        <v>-0.3147088145344539</v>
       </c>
       <c r="K3">
-        <v>-75.8</v>
+        <v>-71.5</v>
       </c>
       <c r="L3">
-        <v>-0.4947780678851175</v>
+        <v>-0.40304396843292</v>
       </c>
       <c r="M3">
-        <v>0.273</v>
+        <v>0.449</v>
       </c>
       <c r="N3">
-        <v>0.0001708278580814718</v>
+        <v>0.0006719545046393296</v>
       </c>
       <c r="O3">
-        <v>-0.003601583113456465</v>
+        <v>-0.00627972027972028</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +758,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0.273</v>
+        <v>0.449</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>65.3</v>
+        <v>52.2</v>
       </c>
       <c r="V3">
-        <v>0.04086102246417621</v>
+        <v>0.07812032325651003</v>
       </c>
       <c r="W3">
-        <v>-1.23051948051948</v>
+        <v>-47.03947368421053</v>
       </c>
       <c r="X3">
-        <v>0.2160435956733699</v>
+        <v>0.1781326523680062</v>
       </c>
       <c r="Y3">
-        <v>-1.44656307619285</v>
+        <v>-47.21760633657853</v>
       </c>
       <c r="Z3">
-        <v>3.070217098478416</v>
+        <v>2.028547901161089</v>
       </c>
       <c r="AA3">
-        <v>-0.716044975756</v>
+        <v>-0.638401905200761</v>
       </c>
       <c r="AB3">
-        <v>0.2048403632329535</v>
+        <v>0.1542949650373791</v>
       </c>
       <c r="AC3">
-        <v>-0.9208853389889535</v>
+        <v>-0.7926968702381401</v>
       </c>
       <c r="AD3">
-        <v>148.2</v>
+        <v>185.3</v>
       </c>
       <c r="AE3">
-        <v>1.963751484357608</v>
+        <v>3.496718492060621</v>
       </c>
       <c r="AF3">
-        <v>150.1637514843576</v>
+        <v>188.7967184920606</v>
       </c>
       <c r="AG3">
-        <v>84.86375148435759</v>
+        <v>136.5967184920606</v>
       </c>
       <c r="AH3">
-        <v>0.08589307612015724</v>
+        <v>0.2203003983775577</v>
       </c>
       <c r="AI3">
-        <v>0.9899791507981212</v>
+        <v>0.8609190314851691</v>
       </c>
       <c r="AJ3">
-        <v>0.0504251808213389</v>
+        <v>0.1697282249708976</v>
       </c>
       <c r="AK3">
-        <v>0.982404098295323</v>
+        <v>0.8174709816252366</v>
       </c>
       <c r="AL3">
-        <v>11.9</v>
+        <v>13.3</v>
       </c>
       <c r="AM3">
-        <v>11.83</v>
+        <v>12.759</v>
       </c>
       <c r="AN3">
-        <v>-4.699242160002536</v>
+        <v>-3.624095442988461</v>
       </c>
       <c r="AO3">
-        <v>-3.016806722689076</v>
+        <v>-4.218045112781954</v>
       </c>
       <c r="AP3">
-        <v>-2.690926577808846</v>
+        <v>-2.671557177626846</v>
       </c>
       <c r="AQ3">
-        <v>-3.034657650042266</v>
+        <v>-4.396896308488126</v>
       </c>
     </row>
   </sheetData>
